--- a/Training/Day3_Calibration/ModelCalibration5Sectorsand1Regions.xlsx
+++ b/Training/Day3_Calibration/ModelCalibration5Sectorsand1Regions.xlsx
@@ -8,15 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\schul\Documents\GitHub\DGE-METRIC\ExcelFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C33272C-E9AA-4A8D-8E7D-019360686274}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{931DBF70-9F1A-4CDF-9959-3720FE0DBD89}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Content" sheetId="4" r:id="rId1"/>
-    <sheet name="Data" sheetId="3" r:id="rId2"/>
-    <sheet name="Start" sheetId="5" r:id="rId3"/>
-    <sheet name="Structural Parameters" sheetId="6" r:id="rId4"/>
+    <sheet name="IO_Data" sheetId="7" r:id="rId2"/>
+    <sheet name="Data" sheetId="3" r:id="rId3"/>
+    <sheet name="Start" sheetId="5" r:id="rId4"/>
+    <sheet name="Structural Parameters" sheetId="6" r:id="rId5"/>
   </sheets>
   <definedNames>
     <definedName name="H0_1_p">Data!$AC$2</definedName>
@@ -140,7 +141,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="611" uniqueCount="401">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="636" uniqueCount="409">
   <si>
     <t>Sheets</t>
   </si>
@@ -1343,6 +1344,30 @@
   </si>
   <si>
     <t>depreciation rate in sector 5 and region 1</t>
+  </si>
+  <si>
+    <t>Intermediate Input Shares and Sectoral Accounts (phiQI, phiX, phiM_I, phiW, phiY0, phiN0)</t>
+  </si>
+  <si>
+    <t>Aggregate Sector</t>
+  </si>
+  <si>
+    <t>Imports Intermediate (phiM_I)</t>
+  </si>
+  <si>
+    <t>Labour (phiW)</t>
+  </si>
+  <si>
+    <t>Value Added (phiY0)</t>
+  </si>
+  <si>
+    <t>Employment Share (phiN0)</t>
+  </si>
+  <si>
+    <t>Intermediate input matrix phiQI [row=using, col=supplying]</t>
+  </si>
+  <si>
+    <t>Final Imports (phiM_F)</t>
   </si>
 </sst>
 </file>
@@ -1353,7 +1378,7 @@
     <numFmt numFmtId="164" formatCode="#,000"/>
     <numFmt numFmtId="165" formatCode="0.000"/>
   </numFmts>
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
@@ -1377,8 +1402,47 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="9"/>
+      <color rgb="FF1F4E79"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="9"/>
+      <color rgb="FF595959"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="13">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1402,8 +1466,48 @@
         <bgColor rgb="FF808080"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F4E79"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD6E4F0"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFF2CC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE2EFDA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFCE4D6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEBF3FA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBDD7EE"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -1411,14 +1515,30 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB8CCE4"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB8CCE4"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB8CCE4"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB8CCE4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="4">
+  <cellStyleXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -1430,12 +1550,59 @@
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="2" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="2"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="4" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="4"/>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="1" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="4" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="4" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="1" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="1" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="1" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="1" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="10" borderId="1" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="11" borderId="1" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="11" borderId="1" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="11" fontId="8" fillId="7" borderId="1" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="11" fontId="8" fillId="8" borderId="1" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="12" borderId="0" xfId="4" applyFont="1" applyFill="1"/>
+    <xf numFmtId="1" fontId="8" fillId="12" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="1" fontId="8" fillId="5" borderId="1" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="4" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="4">
+  <cellStyles count="5">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Neutral 2" xfId="3" xr:uid="{11D8DB23-7D49-4636-AA20-764E78025F5C}"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 2" xfId="2" xr:uid="{C8187110-74C5-456C-92B7-15E58CB65F0F}"/>
+    <cellStyle name="Normal 3" xfId="4" xr:uid="{9F489498-D61F-4269-AF15-0ECF3CF66219}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -1881,6 +2048,312 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{731FB87F-6EB9-4268-A396-07B6CEE9B019}">
+  <dimension ref="A1:L10"/>
+  <sheetFormatPr defaultColWidth="11.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="81.109375" style="12" customWidth="1"/>
+    <col min="2" max="2" width="12" style="12" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.6640625" style="12" customWidth="1"/>
+    <col min="4" max="4" width="14.6640625" style="12" customWidth="1"/>
+    <col min="5" max="7" width="15.6640625" style="12" customWidth="1"/>
+    <col min="8" max="8" width="14.6640625" style="12" customWidth="1"/>
+    <col min="9" max="9" width="25" style="12" customWidth="1"/>
+    <col min="10" max="10" width="15.6640625" style="12" customWidth="1"/>
+    <col min="11" max="11" width="17.109375" style="12" customWidth="1"/>
+    <col min="12" max="12" width="22.33203125" style="12" customWidth="1"/>
+    <col min="13" max="16384" width="11.44140625" style="12"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:12" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="11" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" ht="44.1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="13" t="s">
+        <v>402</v>
+      </c>
+      <c r="B2" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="C2" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2" s="13" t="s">
+        <v>8</v>
+      </c>
+      <c r="E2" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="F2" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="G2" s="13" t="s">
+        <v>11</v>
+      </c>
+      <c r="H2" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="I2" s="13" t="s">
+        <v>403</v>
+      </c>
+      <c r="J2" s="13" t="s">
+        <v>404</v>
+      </c>
+      <c r="K2" s="13" t="s">
+        <v>405</v>
+      </c>
+      <c r="L2" s="13" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" ht="15.9" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="14" t="s">
+        <v>407</v>
+      </c>
+      <c r="H3" s="15"/>
+      <c r="I3" s="15"/>
+      <c r="J3" s="15"/>
+      <c r="K3" s="15"/>
+      <c r="L3" s="15"/>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A4" s="16" t="s">
+        <v>7</v>
+      </c>
+      <c r="B4" s="16" t="s">
+        <v>7</v>
+      </c>
+      <c r="C4" s="17">
+        <v>1.4422226930467616E-2</v>
+      </c>
+      <c r="D4" s="17">
+        <v>3.7320342219725202E-3</v>
+      </c>
+      <c r="E4" s="17">
+        <v>3.6616301746542166E-4</v>
+      </c>
+      <c r="F4" s="17">
+        <v>2.7046072302106115E-2</v>
+      </c>
+      <c r="G4" s="17">
+        <v>4.9752014633807256E-3</v>
+      </c>
+      <c r="H4" s="18">
+        <v>6.9606135777650234E-3</v>
+      </c>
+      <c r="I4" s="19">
+        <v>2.1345398939753808E-2</v>
+      </c>
+      <c r="J4" s="19">
+        <v>3.9525934010030038E-2</v>
+      </c>
+      <c r="K4" s="19">
+        <v>4.3849021879782638E-2</v>
+      </c>
+      <c r="L4" s="20">
+        <v>0.1842193691178716</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A5" s="21" t="s">
+        <v>27</v>
+      </c>
+      <c r="B5" s="21" t="s">
+        <v>8</v>
+      </c>
+      <c r="C5" s="22">
+        <v>6.4131046250132996E-4</v>
+      </c>
+      <c r="D5" s="22">
+        <v>1.1981435075267454E-2</v>
+      </c>
+      <c r="E5" s="22">
+        <v>2.6293620085776073E-4</v>
+      </c>
+      <c r="F5" s="22">
+        <v>3.4208064696140371E-3</v>
+      </c>
+      <c r="G5" s="22">
+        <v>2.664457415963134E-3</v>
+      </c>
+      <c r="H5" s="18">
+        <v>4.6139329963357087E-3</v>
+      </c>
+      <c r="I5" s="19">
+        <v>1.9046009569366043E-2</v>
+      </c>
+      <c r="J5" s="19">
+        <v>6.2225054861662172E-3</v>
+      </c>
+      <c r="K5" s="19">
+        <v>1.8617519651186666E-2</v>
+      </c>
+      <c r="L5" s="20">
+        <v>2.9001364893822636E-2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A6" s="16" t="s">
+        <v>27</v>
+      </c>
+      <c r="B6" s="16" t="s">
+        <v>9</v>
+      </c>
+      <c r="C6" s="23">
+        <v>1.2809840480249971E-5</v>
+      </c>
+      <c r="D6" s="17">
+        <v>1.6536725084701296E-3</v>
+      </c>
+      <c r="E6" s="23">
+        <v>6.7276093480473807E-5</v>
+      </c>
+      <c r="F6" s="17">
+        <v>5.5382681947262744E-4</v>
+      </c>
+      <c r="G6" s="17">
+        <v>3.9025328239636944E-4</v>
+      </c>
+      <c r="H6" s="24">
+        <v>5.9458449010926488E-5</v>
+      </c>
+      <c r="I6" s="19">
+        <v>3.5363100675160186E-4</v>
+      </c>
+      <c r="J6" s="19">
+        <v>7.220402122688162E-4</v>
+      </c>
+      <c r="K6" s="19">
+        <v>3.3232510115607959E-3</v>
+      </c>
+      <c r="L6" s="20">
+        <v>3.3652283168853652E-3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A7" s="21" t="s">
+        <v>10</v>
+      </c>
+      <c r="B7" s="21" t="s">
+        <v>10</v>
+      </c>
+      <c r="C7" s="22">
+        <v>6.8289060727302633E-2</v>
+      </c>
+      <c r="D7" s="22">
+        <v>2.0910080316406104E-2</v>
+      </c>
+      <c r="E7" s="22">
+        <v>3.1774698105269264E-3</v>
+      </c>
+      <c r="F7" s="22">
+        <v>0.33230489238954558</v>
+      </c>
+      <c r="G7" s="22">
+        <v>5.2534316283934832E-2</v>
+      </c>
+      <c r="H7" s="18">
+        <v>0.26208945244385851</v>
+      </c>
+      <c r="I7" s="19">
+        <v>0.18111130931207689</v>
+      </c>
+      <c r="J7" s="19">
+        <v>7.6328942267527067E-2</v>
+      </c>
+      <c r="K7" s="19">
+        <v>0.11242207494191821</v>
+      </c>
+      <c r="L7" s="20">
+        <v>0.35574793972964974</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A8" s="16" t="s">
+        <v>11</v>
+      </c>
+      <c r="B8" s="16" t="s">
+        <v>11</v>
+      </c>
+      <c r="C8" s="17">
+        <v>5.8979093180920004E-3</v>
+      </c>
+      <c r="D8" s="17">
+        <v>1.2874786907895341E-2</v>
+      </c>
+      <c r="E8" s="17">
+        <v>1.5030145154121396E-3</v>
+      </c>
+      <c r="F8" s="17">
+        <v>3.715440122175153E-2</v>
+      </c>
+      <c r="G8" s="17">
+        <v>5.0678527879484805E-2</v>
+      </c>
+      <c r="H8" s="18">
+        <v>3.3650860704118872E-2</v>
+      </c>
+      <c r="I8" s="19">
+        <v>2.5526241462421551E-2</v>
+      </c>
+      <c r="J8" s="19">
+        <v>9.1759634432129741E-2</v>
+      </c>
+      <c r="K8" s="19">
+        <v>0.15231984492284562</v>
+      </c>
+      <c r="L8" s="20">
+        <v>0.42766609794177063</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" ht="5.0999999999999996" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="25"/>
+      <c r="B9" s="25"/>
+      <c r="C9" s="26"/>
+      <c r="D9" s="26"/>
+      <c r="E9" s="26"/>
+      <c r="F9" s="26"/>
+      <c r="G9" s="26"/>
+      <c r="H9" s="26"/>
+      <c r="I9" s="26"/>
+      <c r="J9" s="26"/>
+      <c r="K9" s="26"/>
+      <c r="L9" s="27"/>
+    </row>
+    <row r="10" spans="1:12" ht="15.9" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="28" t="s">
+        <v>408</v>
+      </c>
+      <c r="C10" s="18">
+        <v>3.5541008973436171E-3</v>
+      </c>
+      <c r="D10" s="18">
+        <v>1.6303336010453947E-3</v>
+      </c>
+      <c r="E10" s="24">
+        <v>1.2434776358848521E-5</v>
+      </c>
+      <c r="F10" s="18">
+        <v>3.8262887217700513E-2</v>
+      </c>
+      <c r="G10" s="18">
+        <v>3.1851583840066203E-3</v>
+      </c>
+      <c r="H10" s="27"/>
+      <c r="I10" s="27"/>
+      <c r="J10" s="27"/>
+      <c r="K10" s="27"/>
+      <c r="L10" s="27"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{17426F49-91B6-4949-8BDD-64026552C6AA}">
   <dimension ref="A1:AL21"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -2647,7 +3120,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{102D4A06-FE13-4A37-8710-AC4CD239418C}">
   <dimension ref="A1:C43"/>
   <sheetFormatPr defaultColWidth="8.5546875" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.3"/>
@@ -3111,7 +3584,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0CC00773-2217-4A15-8F36-7940A6632C72}">
   <dimension ref="A1:D158"/>
   <sheetFormatPr defaultColWidth="8.5546875" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.3"/>
@@ -4791,6 +5264,13 @@
     </row>
   </sheetData>
   <mergeCells count="19">
+    <mergeCell ref="A153:C153"/>
+    <mergeCell ref="A87:C87"/>
+    <mergeCell ref="A93:C93"/>
+    <mergeCell ref="A99:C99"/>
+    <mergeCell ref="A120:C120"/>
+    <mergeCell ref="A141:C141"/>
+    <mergeCell ref="A147:C147"/>
     <mergeCell ref="A81:C81"/>
     <mergeCell ref="A15:C15"/>
     <mergeCell ref="A21:C21"/>
@@ -4803,13 +5283,6 @@
     <mergeCell ref="A63:C63"/>
     <mergeCell ref="A69:C69"/>
     <mergeCell ref="A75:C75"/>
-    <mergeCell ref="A153:C153"/>
-    <mergeCell ref="A87:C87"/>
-    <mergeCell ref="A93:C93"/>
-    <mergeCell ref="A99:C99"/>
-    <mergeCell ref="A120:C120"/>
-    <mergeCell ref="A141:C141"/>
-    <mergeCell ref="A147:C147"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
